--- a/output/2026-09-16_FOMC日盤中掃描_低波幅10分鐘均線.xlsx
+++ b/output/2026-09-16_FOMC日盤中掃描_低波幅10分鐘均線.xlsx
@@ -192,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -297,6 +297,24 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -860,7 +878,7 @@
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>黃金</t>
         </is>
@@ -1046,12 +1064,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>道指</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>+0.15%</t>
         </is>
@@ -1059,12 +1077,12 @@
       <c r="C5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>納指</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>+0.44%</t>
         </is>
@@ -1110,12 +1128,12 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Brent 原油</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>$106.47 (+2.07%)</t>
         </is>
@@ -1132,7 +1150,7 @@
           <t>WTI 原油</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>$101.88 (+1.9%)</t>
         </is>
@@ -1157,12 +1175,12 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>黃金</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>跌穿 $4,300</t>
         </is>
@@ -1174,12 +1192,12 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>跌逾 2%</t>
         </is>
@@ -1196,7 +1214,7 @@
           <t>費城半導體指數（昨日）</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>-5.9%</t>
         </is>
@@ -1208,12 +1226,12 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>約 $141</t>
         </is>
@@ -1414,7 +1432,7 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>10:00–11:00</t>
         </is>
@@ -1448,7 +1466,7 @@
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>11:30–13:30</t>
         </is>
@@ -1483,7 +1501,7 @@
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
@@ -1519,7 +1537,7 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>15:00–16:00</t>
         </is>
@@ -1536,7 +1554,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>盤後 / 隔夜</t>
         </is>
@@ -1612,7 +1630,7 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>續跌</t>
         </is>
@@ -1629,7 +1647,7 @@
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>深度修正</t>
         </is>
@@ -1646,7 +1664,7 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>期中年型態</t>
         </is>
@@ -1917,7 +1935,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>原地已加連結的儲存格：13 個。另有 6 個儲存格同時提及多個代號 —— Excel 不支援在單一儲存格內為部分文字加連結，故該類儲存格不在原地處理，改由本表覆蓋。點擊下方連結即可開啟該代號的 TradingView 圖表。</t>
+          <t>原地已加連結的儲存格：0 個。另有 6 個儲存格同時提及多個代號 —— Excel 不支援在單一儲存格內為部分文字加連結，故該類儲存格不在原地處理，改由本表覆蓋。點擊下方連結即可開啟該代號的 TradingView 圖表。</t>
         </is>
       </c>
     </row>
@@ -1944,17 +1962,17 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>NASDAQ:AMD</t>
         </is>
@@ -1966,17 +1984,17 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="42" t="inlineStr">
         <is>
           <t>NASDAQ:AMZN</t>
         </is>
@@ -1988,17 +2006,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>Broadcom</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
         <is>
           <t>NASDAQ:AVGO</t>
         </is>
@@ -2010,17 +2028,17 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Chevron</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
         <is>
           <t>NYSE:CVX</t>
         </is>
@@ -2032,17 +2050,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Alphabet</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>NASDAQ:GOOGL</t>
         </is>
@@ -2054,17 +2072,17 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>IXIC</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>納斯達克綜合指數</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="42" t="inlineStr">
         <is>
           <t>NASDAQ:IXIC</t>
         </is>
@@ -2076,17 +2094,17 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>NASDAQ:MSFT</t>
         </is>
@@ -2098,17 +2116,17 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="42" t="inlineStr">
         <is>
           <t>NASDAQ:NVDA</t>
         </is>
@@ -2120,17 +2138,17 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="39" t="inlineStr">
         <is>
           <t>NYSE:ORCL</t>
         </is>
@@ -2142,17 +2160,17 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="41" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="42" t="inlineStr">
         <is>
           <t>NYSE:XOM</t>
         </is>
@@ -2164,17 +2182,17 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>DJI</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>道瓊工業指數</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="39" t="inlineStr">
         <is>
           <t>DJ:DJI</t>
         </is>
@@ -2186,17 +2204,17 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>GOLD</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>黃金現貨</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="42" t="inlineStr">
         <is>
           <t>TVC:GOLD</t>
         </is>
@@ -2208,17 +2226,17 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>RUT</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>羅素 2000 指數</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="39" t="inlineStr">
         <is>
           <t>TVC:RUT</t>
         </is>
@@ -2230,17 +2248,17 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>標普 500 指數</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>SP:SPX</t>
         </is>
@@ -2252,17 +2270,17 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>UKOIL</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>Brent 原油</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="39" t="inlineStr">
         <is>
           <t>TVC:UKOIL</t>
         </is>
@@ -2274,17 +2292,17 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>US10Y</t>
         </is>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>美國 10 年期孳息</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>TVC:US10Y</t>
         </is>

--- a/output/2026-09-16_FOMC日盤中掃描_低波幅10分鐘均線.xlsx
+++ b/output/2026-09-16_FOMC日盤中掃描_低波幅10分鐘均線.xlsx
@@ -192,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -297,6 +297,60 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -878,7 +932,7 @@
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>黃金</t>
         </is>
@@ -1064,12 +1118,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>道指</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>+0.15%</t>
         </is>
@@ -1077,12 +1131,12 @@
       <c r="C5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>納指</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>+0.44%</t>
         </is>
@@ -1128,12 +1182,12 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Brent 原油</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>$106.47 (+2.07%)</t>
         </is>
@@ -1150,7 +1204,7 @@
           <t>WTI 原油</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>$101.88 (+1.9%)</t>
         </is>
@@ -1175,12 +1229,12 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>黃金</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>跌穿 $4,300</t>
         </is>
@@ -1192,12 +1246,12 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>跌逾 2%</t>
         </is>
@@ -1214,7 +1268,7 @@
           <t>費城半導體指數（昨日）</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>-5.9%</t>
         </is>
@@ -1226,12 +1280,12 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>約 $141</t>
         </is>
@@ -1432,7 +1486,7 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>10:00–11:00</t>
         </is>
@@ -1466,7 +1520,7 @@
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>11:30–13:30</t>
         </is>
@@ -1501,7 +1555,7 @@
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
@@ -1537,7 +1591,7 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>15:00–16:00</t>
         </is>
@@ -1554,7 +1608,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>盤後 / 隔夜</t>
         </is>
@@ -1630,7 +1684,7 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="49" t="inlineStr">
         <is>
           <t>續跌</t>
         </is>
@@ -1647,7 +1701,7 @@
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>深度修正</t>
         </is>
@@ -1664,7 +1718,7 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="49" t="inlineStr">
         <is>
           <t>期中年型態</t>
         </is>
@@ -1962,17 +2016,17 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="57" t="inlineStr">
         <is>
           <t>NASDAQ:AMD</t>
         </is>
@@ -1984,17 +2038,17 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>NASDAQ:AMZN</t>
         </is>
@@ -2006,17 +2060,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>Broadcom</t>
         </is>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="C7" s="57" t="inlineStr">
         <is>
           <t>NASDAQ:AVGO</t>
         </is>
@@ -2028,17 +2082,17 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Chevron</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>NYSE:CVX</t>
         </is>
@@ -2050,17 +2104,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>Alphabet</t>
         </is>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="57" t="inlineStr">
         <is>
           <t>NASDAQ:GOOGL</t>
         </is>
@@ -2072,17 +2126,17 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>IXIC</t>
         </is>
       </c>
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>納斯達克綜合指數</t>
         </is>
       </c>
-      <c r="C10" s="42" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>NASDAQ:IXIC</t>
         </is>
@@ -2094,17 +2148,17 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="C11" s="39" t="inlineStr">
+      <c r="C11" s="57" t="inlineStr">
         <is>
           <t>NASDAQ:MSFT</t>
         </is>
@@ -2116,17 +2170,17 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C12" s="42" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>NASDAQ:NVDA</t>
         </is>
@@ -2138,17 +2192,17 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="56" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="C13" s="39" t="inlineStr">
+      <c r="C13" s="57" t="inlineStr">
         <is>
           <t>NYSE:ORCL</t>
         </is>
@@ -2160,17 +2214,17 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="C14" s="42" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>NYSE:XOM</t>
         </is>
@@ -2182,17 +2236,17 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="55" t="inlineStr">
         <is>
           <t>DJI</t>
         </is>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="56" t="inlineStr">
         <is>
           <t>道瓊工業指數</t>
         </is>
       </c>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="C15" s="57" t="inlineStr">
         <is>
           <t>DJ:DJI</t>
         </is>
@@ -2204,17 +2258,17 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>GOLD</t>
         </is>
       </c>
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>黃金現貨</t>
         </is>
       </c>
-      <c r="C16" s="42" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>TVC:GOLD</t>
         </is>
@@ -2226,17 +2280,17 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="55" t="inlineStr">
         <is>
           <t>RUT</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="56" t="inlineStr">
         <is>
           <t>羅素 2000 指數</t>
         </is>
       </c>
-      <c r="C17" s="39" t="inlineStr">
+      <c r="C17" s="57" t="inlineStr">
         <is>
           <t>TVC:RUT</t>
         </is>
@@ -2248,17 +2302,17 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A18" s="58" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="B18" s="41" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>標普 500 指數</t>
         </is>
       </c>
-      <c r="C18" s="42" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>SP:SPX</t>
         </is>
@@ -2270,17 +2324,17 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="55" t="inlineStr">
         <is>
           <t>UKOIL</t>
         </is>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="56" t="inlineStr">
         <is>
           <t>Brent 原油</t>
         </is>
       </c>
-      <c r="C19" s="39" t="inlineStr">
+      <c r="C19" s="57" t="inlineStr">
         <is>
           <t>TVC:UKOIL</t>
         </is>
@@ -2292,17 +2346,17 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>US10Y</t>
         </is>
       </c>
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>美國 10 年期孳息</t>
         </is>
       </c>
-      <c r="C20" s="42" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>TVC:US10Y</t>
         </is>
